--- a/templates/INVENTORY_REPORT_TEMPLATE.xlsx
+++ b/templates/INVENTORY_REPORT_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -80,10 +80,10 @@
     <t>350100000007919</t>
   </si>
   <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>eSIM</t>
+    <t>ONU</t>
+  </si>
+  <si>
+    <t>Physical SIM + eSIM</t>
   </si>
   <si>
     <t>STARLIGHT</t>
@@ -101,7 +101,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>Dual SIM</t>
+    <t>Dual Physical SIM</t>
   </si>
   <si>
     <t>GREEN</t>
@@ -143,6 +143,9 @@
     <t>350100000031676</t>
   </si>
   <si>
+    <t>Brand new</t>
+  </si>
+  <si>
     <t>BLACK</t>
   </si>
   <si>
@@ -200,10 +203,10 @@
     <t>The unique key for the unit. An existing IMEI updates that unit rather than creating a duplicate. Invalid IMEIs are listed in the preview and skipped.</t>
   </si>
   <si>
-    <t>A+, A, B+, B, C</t>
-  </si>
-  <si>
-    <t>Condition grade. Free text is accepted, but sticking to the dropdown keeps reports groupable.</t>
+    <t>A, B, C, ONU, Brand new</t>
+  </si>
+  <si>
+    <t>Condition grade — exactly the options the Add Stock screen offers. ONU = Open Never Used. Free text is accepted, but sticking to the dropdown keeps reports groupable.</t>
   </si>
   <si>
     <t>e.g. 64GB, 128GB, 256GB, 1TB</t>
@@ -212,10 +215,10 @@
     <t>Used with Model to form the SKU. If omitted it is parsed out of Model when present there.</t>
   </si>
   <si>
-    <t>Physical SIM, eSIM, Dual SIM, Not Applicable</t>
-  </si>
-  <si>
-    <t>Recorded on the unit and shown in the stock overlays.</t>
+    <t>Physical SIM, Physical SIM + eSIM, Dual Physical SIM, Not Applicable</t>
+  </si>
+  <si>
+    <t>Recorded on the unit and shown in the stock overlays. The app also allows a free-text "Other".</t>
   </si>
   <si>
     <t>Free text, e.g. MIDNIGHT</t>
@@ -882,7 +885,7 @@
         <v>42</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>15</v>
@@ -891,10 +894,10 @@
         <v>23</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6" s="8">
         <v>275</v>
@@ -1404,16 +1407,16 @@
   <autoFilter ref="A1:K1"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" sqref="D10:D500">
-      <formula1>"A+,A,B+,B,C"</formula1>
+      <formula1>"A,B,C,ONU,Brand new"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500">
-      <formula1>"A+,A,B+,B,C"</formula1>
+      <formula1>"A,B,C,ONU,Brand new"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F10:F500">
-      <formula1>"Physical SIM,eSIM,Dual SIM,Not Applicable"</formula1>
+      <formula1>"Physical SIM,Physical SIM + eSIM,Dual Physical SIM,Not Applicable"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F2:F500">
-      <formula1>"Physical SIM,eSIM,Dual SIM,Not Applicable"</formula1>
+      <formula1>"Physical SIM,Physical SIM + eSIM,Dual Physical SIM,Not Applicable"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="J10:J500">
       <formula1>"OFFICE,SHS"</formula1>
@@ -1443,41 +1446,41 @@
   <sheetData>
     <row r="1" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,13 +1502,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1513,13 +1516,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,13 +1530,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1541,13 +1544,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,13 +1558,13 @@
         <v>5</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,13 +1572,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,13 +1586,13 @@
         <v>7</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,13 +1600,13 @@
         <v>8</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,13 +1614,13 @@
         <v>9</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1625,13 +1628,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/templates/INVENTORY_REPORT_TEMPLATE.xlsx
+++ b/templates/INVENTORY_REPORT_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="79">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -116,9 +116,6 @@
     <t>IPHONE 13 PRO</t>
   </si>
   <si>
-    <t>350100000023757</t>
-  </si>
-  <si>
     <t>256GB</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>GOOGLE PIXEL 7</t>
   </si>
   <si>
-    <t>350100000031676</t>
-  </si>
-  <si>
     <t>Brand new</t>
   </si>
   <si>
@@ -167,6 +161,9 @@
     <t>An IMEI already in the system UPDATES that unit; a new IMEI CREATES one. Re-uploading the same file is safe.</t>
   </si>
   <si>
+    <t>SHS rows leave IMEI BLANK — supplier-held stock has not shipped, so there is no IMEI yet. It is captured when you Receive the unit.</t>
+  </si>
+  <si>
     <t>Column</t>
   </si>
   <si>
@@ -197,10 +194,13 @@
     <t>Brand and storage are parsed out of this string where possible. Keep it consistent — it is how stock groups together across the app.</t>
   </si>
   <si>
+    <t>Office only</t>
+  </si>
+  <si>
     <t>15 digits, or a 10-12 character Apple serial</t>
   </si>
   <si>
-    <t>The unique key for the unit. An existing IMEI updates that unit rather than creating a duplicate. Invalid IMEIs are listed in the preview and skipped.</t>
+    <t>The unique key for the unit. An existing IMEI updates that unit rather than creating a duplicate. REQUIRED for OFFICE stock; leave BLANK for SHS — supplier-held stock has not shipped, so there is no IMEI to record yet. It is captured on Receive. Invalid IMEIs are listed in the preview and skipped.</t>
   </si>
   <si>
     <t>A, B, C, ONU, Brand new</t>
@@ -847,45 +847,45 @@
         <v>33</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="I5" s="8">
         <v>520</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>15</v>
@@ -894,19 +894,19 @@
         <v>23</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I6" s="8">
         <v>275</v>
       </c>
       <c r="J6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="4:10" x14ac:dyDescent="0.25"/>
@@ -1435,7 +1435,7 @@
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1446,194 +1446,199 @@
   <sheetData>
     <row r="1" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="B9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C9" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>61</v>
-      </c>
       <c r="D11" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>58</v>
+        <v>6</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>55</v>
+        <v>8</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>57</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="B20" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>78</v>
       </c>
     </row>
